--- a/reviews/REVIEWED_StateRepHong_20210107_20210317_20260806_autoPush.xlsx
+++ b/reviews/REVIEWED_StateRepHong_20210107_20210317_20260806_autoPush.xlsx
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="inlineStr"/>
     </row>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="inlineStr"/>
     </row>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr"/>
     </row>

--- a/reviews/REVIEWED_StateRepHong_20210107_20210317_20260806_autoPush.xlsx
+++ b/reviews/REVIEWED_StateRepHong_20210107_20210317_20260806_autoPush.xlsx
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr"/>
     </row>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="inlineStr"/>
     </row>

--- a/reviews/REVIEWED_StateRepHong_20210107_20210317_20260806_autoPush.xlsx
+++ b/reviews/REVIEWED_StateRepHong_20210107_20210317_20260806_autoPush.xlsx
@@ -3728,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="inlineStr"/>
     </row>
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="inlineStr"/>
     </row>

--- a/reviews/REVIEWED_StateRepHong_20210107_20210317_20260806_autoPush.xlsx
+++ b/reviews/REVIEWED_StateRepHong_20210107_20210317_20260806_autoPush.xlsx
@@ -3814,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="inlineStr"/>
     </row>
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="inlineStr"/>
     </row>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="inlineStr"/>
     </row>
